--- a/data/05_modelado/results/results_arboles.xlsx
+++ b/data/05_modelado/results/results_arboles.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -542,52 +542,52 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7580137134565823</v>
+        <v>0.8169909203107798</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005482087979962167</v>
+        <v>0.00403007160636598</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9255995216415347</v>
+        <v>0.9472837262589477</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003787021573586583</v>
+        <v>0.002751049853717754</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8572283564913865</v>
+        <v>0.8060355566987134</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6796328772301973</v>
+        <v>0.8285014511882942</v>
       </c>
       <c r="J2" t="n">
-        <v>0.873103698743081</v>
+        <v>0.8914335247012511</v>
       </c>
       <c r="K2" t="n">
-        <v>36.396</v>
+        <v>78.515</v>
       </c>
       <c r="L2" t="n">
-        <v>5.14</v>
+        <v>6.64</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7693</v>
+        <v>0.8174</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9308</v>
+        <v>0.95</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8537</v>
+        <v>0.7942</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.8419</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8772</v>
+        <v>0.89</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6867</v>
+        <v>0.7387</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3002</v>
+        <v>0.2706</v>
       </c>
     </row>
     <row r="3">
@@ -598,7 +598,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -607,52 +607,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7787225159442722</v>
+        <v>0.8119230545151636</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005997512743632617</v>
+        <v>0.003672167353116909</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9250778506279677</v>
+        <v>0.9468460134581385</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003443392487008852</v>
+        <v>0.003213222126478196</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7592287863582301</v>
+        <v>0.8745186228742853</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7993887480199137</v>
+        <v>0.7579444582216905</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8671547827120614</v>
+        <v>0.8973080152679669</v>
       </c>
       <c r="K3" t="n">
-        <v>16.146</v>
+        <v>22.354</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7851</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9296</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7522</v>
+        <v>0.8622</v>
       </c>
       <c r="P3" t="n">
-        <v>0.821</v>
+        <v>0.7728</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8686</v>
+        <v>0.8974</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6907</v>
+        <v>0.7443</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3284</v>
+        <v>0.2576</v>
       </c>
     </row>
     <row r="4">
@@ -663,7 +663,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>smote</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -672,52 +672,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7782213124346666</v>
+        <v>0.8120138369716026</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006809658645278932</v>
+        <v>0.006330304171625894</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9240604004900707</v>
+        <v>0.9463225401639883</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003663125512128296</v>
+        <v>0.002890365512650833</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7740562378479641</v>
+        <v>0.7843580412773777</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7826072275881678</v>
+        <v>0.841849879357099</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8695714505881679</v>
+        <v>0.8860051515220626</v>
       </c>
       <c r="K4" t="n">
-        <v>15.915</v>
+        <v>14.862</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7831</v>
+        <v>0.8159</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9288</v>
+        <v>0.9497</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7775</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7992</v>
+        <v>0.8582</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.8867</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6908</v>
+        <v>0.7343</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3168</v>
+        <v>0.2805</v>
       </c>
     </row>
     <row r="5">
@@ -728,7 +728,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -737,52 +737,52 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7449095387311913</v>
+        <v>0.7591554666450639</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007181450334187754</v>
+        <v>0.006986982179453731</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9064751028619534</v>
+        <v>0.9315129619923168</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004133827840274739</v>
+        <v>0.00376073451208329</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7081655179884478</v>
+        <v>0.8768327532554583</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7859125280402859</v>
+        <v>0.6695891840630204</v>
       </c>
       <c r="J5" t="n">
-        <v>0.842615755474788</v>
+        <v>0.8757806104007668</v>
       </c>
       <c r="K5" t="n">
-        <v>7.072</v>
+        <v>35.522</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7564</v>
+        <v>0.761</v>
       </c>
       <c r="N5" t="n">
-        <v>0.913</v>
+        <v>0.9336</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7065</v>
+        <v>0.8643</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8139</v>
+        <v>0.6797</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8467</v>
+        <v>0.8751</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6454</v>
+        <v>0.678</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4136</v>
+        <v>0.3122</v>
       </c>
     </row>
     <row r="6">
@@ -793,7 +793,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>smote</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -802,52 +802,52 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7441482098143479</v>
+        <v>0.7810657033018569</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007615210426067979</v>
+        <v>0.007559627176103657</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9052964237555472</v>
+        <v>0.9313679768742575</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003862990540722517</v>
+        <v>0.003516553961544682</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7178071943882411</v>
+        <v>0.7330423223469913</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7726911646745307</v>
+        <v>0.836002959729424</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8446234875956409</v>
+        <v>0.8629535208863327</v>
       </c>
       <c r="K6" t="n">
-        <v>7.963</v>
+        <v>2.793</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7532</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9119</v>
+        <v>0.9343</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7155</v>
+        <v>0.7221</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7951</v>
+        <v>0.8546</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8476</v>
+        <v>0.8613</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6434</v>
+        <v>0.6819</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4106</v>
+        <v>0.3506</v>
       </c>
     </row>
     <row r="7">
@@ -858,7 +858,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -867,52 +867,52 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.676398143613919</v>
+        <v>0.783444623490177</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01150729959634567</v>
+        <v>0.009242881824032642</v>
       </c>
       <c r="F7" t="n">
-        <v>0.905201441677766</v>
+        <v>0.9308044637766206</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004635262884190471</v>
+        <v>0.003272936094553819</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8836132567534383</v>
+        <v>0.7465855429302748</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5481809053831694</v>
+        <v>0.8243067778934707</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8467057142916381</v>
+        <v>0.8667458469568079</v>
       </c>
       <c r="K7" t="n">
-        <v>6.286</v>
+        <v>34.249</v>
       </c>
       <c r="L7" t="n">
-        <v>5.14</v>
+        <v>6.65</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6938</v>
+        <v>0.785</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9129</v>
+        <v>0.9332</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8804</v>
+        <v>0.7346</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5724</v>
+        <v>0.8429</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8522</v>
+        <v>0.865</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6021</v>
+        <v>0.6873</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3661</v>
+        <v>0.3451</v>
       </c>
     </row>
     <row r="8">
@@ -923,7 +923,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,52 +932,52 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6921021153867956</v>
+        <v>0.7493470312335072</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01337270905694012</v>
+        <v>0.006349929513041751</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8717836427536556</v>
+        <v>0.9057562632928381</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009995687307184685</v>
+        <v>0.003212375345637456</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6256096023463031</v>
+        <v>0.6980245716132399</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7749780887934983</v>
+        <v>0.8090520545643567</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7984453585504969</v>
+        <v>0.8416865049334774</v>
       </c>
       <c r="K8" t="n">
-        <v>7.777</v>
+        <v>16.298</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7074</v>
+        <v>0.7613</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8709</v>
+        <v>0.9072</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.7294</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7651</v>
+        <v>0.7961</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8149</v>
+        <v>0.854</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.6564</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5194</v>
+        <v>0.3845</v>
       </c>
     </row>
     <row r="9">
@@ -997,52 +997,52 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6667710064068929</v>
+        <v>0.7361697829446927</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01894239180031032</v>
+        <v>0.01112601087569545</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8629433668971502</v>
+        <v>0.9026765293335541</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01097309759275986</v>
+        <v>0.004878767896935301</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7489098357091311</v>
+        <v>0.7754078384204025</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6031004458173224</v>
+        <v>0.7015024827315458</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8242860677382993</v>
+        <v>0.8530261771131158</v>
       </c>
       <c r="K9" t="n">
-        <v>2.818</v>
+        <v>2.588</v>
       </c>
       <c r="L9" t="n">
-        <v>5.32</v>
+        <v>6.91</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.9109</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7973</v>
+        <v>0.8228</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6019</v>
+        <v>0.668</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8388</v>
+        <v>0.8608</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5804</v>
+        <v>0.6441</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4128</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="10">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>smote</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1062,52 +1062,52 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6897703602942326</v>
+        <v>0.7329380126007593</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02240601914767313</v>
+        <v>0.009663686372255531</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8587799720113086</v>
+        <v>0.8999538184092056</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01610594815560971</v>
+        <v>0.003311414395632856</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6453804703360848</v>
+        <v>0.6545947385865329</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7414163403882708</v>
+        <v>0.8347279496522884</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8049520889097144</v>
+        <v>0.8217955618400345</v>
       </c>
       <c r="K10" t="n">
-        <v>10.122</v>
+        <v>2.813</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7007</v>
+        <v>0.7453</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8703</v>
+        <v>0.9133</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6685</v>
+        <v>0.6617</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7361</v>
+        <v>0.8531</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8161</v>
+        <v>0.8294</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5684</v>
+        <v>0.6201</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4682</v>
+        <v>0.4213</v>
       </c>
     </row>
   </sheetData>
